--- a/events/Duisburg_2010_WC/Duisburg_2010_WC_Results.xlsx
+++ b/events/Duisburg_2010_WC/Duisburg_2010_WC_Results.xlsx
@@ -3744,11 +3744,6 @@
           <t>0:44.647</t>
         </is>
       </c>
-      <c r="R53" t="inlineStr">
-        <is>
-          <t>133041</t>
-        </is>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -16948,11 +16943,6 @@
           <t>3:21.389</t>
         </is>
       </c>
-      <c r="R263" t="inlineStr">
-        <is>
-          <t>41785</t>
-        </is>
-      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -17668,11 +17658,6 @@
           <t>1:38.123</t>
         </is>
       </c>
-      <c r="S274" t="inlineStr">
-        <is>
-          <t>133041</t>
-        </is>
-      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -22273,11 +22258,6 @@
           <t>0:44.931</t>
         </is>
       </c>
-      <c r="R346" t="inlineStr">
-        <is>
-          <t>133041</t>
-        </is>
-      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -37997,11 +37977,6 @@
           <t>3:16.555</t>
         </is>
       </c>
-      <c r="R593" t="inlineStr">
-        <is>
-          <t>41785</t>
-        </is>
-      </c>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
@@ -38559,11 +38534,6 @@
           <t>1:36.651</t>
         </is>
       </c>
-      <c r="S602" t="inlineStr">
-        <is>
-          <t>133041</t>
-        </is>
-      </c>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
@@ -43799,11 +43769,6 @@
           <t>3:19.525</t>
         </is>
       </c>
-      <c r="R682" t="inlineStr">
-        <is>
-          <t>41785</t>
-        </is>
-      </c>
     </row>
     <row r="683">
       <c r="A683" t="inlineStr">
@@ -44755,11 +44720,6 @@
       <c r="P696" t="inlineStr">
         <is>
           <t>1:41.745</t>
-        </is>
-      </c>
-      <c r="S696" t="inlineStr">
-        <is>
-          <t>133041</t>
         </is>
       </c>
     </row>
@@ -73519,7 +73479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D143"/>
+  <dimension ref="A1:D141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73899,39 +73859,39 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>41785</t>
+          <t>35813</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Olivier</t>
+          <t>Rachel</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CAUWENBERGH</t>
+          <t>CAWTHORN</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>35813</t>
+          <t>50186</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Rachel</t>
+          <t>Stefania</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CAWTHORN</t>
+          <t>CICALI</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -73943,39 +73903,39 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>50186</t>
+          <t>45846</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Stefania</t>
+          <t>Jacob</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CICALI</t>
+          <t>CLEAR</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>45846</t>
+          <t>42449</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Jacob</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CLEAR</t>
+          <t>COCHRANE</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -73987,61 +73947,61 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>42449</t>
+          <t>56351</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Valdenice</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>COCHRANE</t>
+          <t>CONCEICAO DO NASCIMENTO</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>56351</t>
+          <t>47443</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Valdenice</t>
+          <t>Dan Cristian</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CONCEICAO DO NASCIMENTO</t>
+          <t>COSTEA</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>47443</t>
+          <t>36231</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Dan Cristian</t>
+          <t>Andrew</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>COSTEA</t>
+          <t>DANIELS</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -74053,17 +74013,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>36231</t>
+          <t>42262</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Andrew</t>
+          <t>Cesar</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>DANIELS</t>
+          <t>DE CESARE</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -74075,17 +74035,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>42262</t>
+          <t>42571</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Cesar</t>
+          <t>Alexey</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>DE CESARE</t>
+          <t>DERGUNOV</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -74097,61 +74057,61 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>42571</t>
+          <t>35700</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Alexey</t>
+          <t>Tina</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>DERGUNOV</t>
+          <t>DIETZE</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>35700</t>
+          <t>47253</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Tina</t>
+          <t>Liviu Alexandru</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>DIETZE</t>
+          <t>DUMITRESCU LAZAR</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>47253</t>
+          <t>42798</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Liviu Alexandru</t>
+          <t>Peter</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>DUMITRESCU LAZAR</t>
+          <t>EGAN</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -74163,39 +74123,39 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>42798</t>
+          <t>42337</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Peter</t>
+          <t>Henriette Engel</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>EGAN</t>
+          <t>HANSEN</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>42337</t>
+          <t>47792</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Henriette Engel</t>
+          <t>Ariel</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>HANSEN</t>
+          <t>FARRAR-WELLMAN</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -74207,17 +74167,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>47792</t>
+          <t>42173</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Ariel</t>
+          <t>Naomi</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>FARRAR-WELLMAN</t>
+          <t>FLOOD</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -74229,56 +74189,56 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>42173</t>
+          <t>35927</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Naomi</t>
+          <t>Pawel</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>FLOOD</t>
+          <t>FLORCZAK</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>35927</t>
+          <t>42453</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Pawel</t>
+          <t>Emilie</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>FLORCZAK</t>
+          <t>FOURNEL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>42453</t>
+          <t>42455</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Emilie</t>
+          <t>Hughes</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -74288,24 +74248,24 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>42455</t>
+          <t>47596</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Hughes</t>
+          <t>Petrus</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>FOURNEL</t>
+          <t>GAVRILA</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -74317,17 +74277,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>47596</t>
+          <t>75776</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Petrus</t>
+          <t>Matthew</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>GAVRILA</t>
+          <t>GOBLE</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -74339,17 +74299,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>75776</t>
+          <t>56336</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Matthew</t>
+          <t>Vyacheslav</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>GOBLE</t>
+          <t>GORN</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -74361,17 +74321,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>56336</t>
+          <t>35705</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Vyacheslav</t>
+          <t>Marcus</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>GORN</t>
+          <t>GROSS</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -74383,17 +74343,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>35705</t>
+          <t>35876</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Marcus</t>
+          <t>Marcin</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>GROSS</t>
+          <t>GRZYBOWSKI</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -74405,17 +74365,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>35876</t>
+          <t>64492</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Marcin</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>GRZYBOWSKI</t>
+          <t>HALL</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -74427,105 +74387,105 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>64492</t>
+          <t>36220</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Angela</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>HALL</t>
+          <t>HANNAH</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>36220</t>
+          <t>42514</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Angela</t>
+          <t>Gordan</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>HANNAH</t>
+          <t>HARBRECHT</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>42514</t>
+          <t>36391</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Gordan</t>
+          <t>Bridgitte</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>HARBRECHT</t>
+          <t>HARTLEY</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>36391</t>
+          <t>36228</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Bridgitte</t>
+          <t>Liam</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>HARTLEY</t>
+          <t>HEATH</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>36228</t>
+          <t>35707</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Liam</t>
+          <t>Max</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>HEATH</t>
+          <t>HOFF</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -74537,61 +74497,61 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>35707</t>
+          <t>42360</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Max</t>
+          <t>Margaret</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>HOFF</t>
+          <t>HOGAN</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>42360</t>
+          <t>52230</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Margaret</t>
+          <t>Mirziyodjon</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>HOGAN</t>
+          <t>KHOJIEV</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>52230</t>
+          <t>35708</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Mirziyodjon</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>KHOJIEV</t>
+          <t>HOLLSTEIN</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -74603,17 +74563,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>35708</t>
+          <t>42336</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Rene Holten</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>HOLLSTEIN</t>
+          <t>POULSEN</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -74625,17 +74585,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>42336</t>
+          <t>35709</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Rene Holten</t>
+          <t>Stefan</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>POULSEN</t>
+          <t>HOLTZ</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -74647,17 +74607,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>35709</t>
+          <t>42358</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Stefan</t>
+          <t>Timothy</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>HOLTZ</t>
+          <t>HORNSBY</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -74669,61 +74629,61 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>42358</t>
+          <t>42260</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Timothy</t>
+          <t>Belen</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>HORNSBY</t>
+          <t>IBARRA</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>42260</t>
+          <t>69073</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Belen</t>
+          <t>Vilyam</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>IBARRA</t>
+          <t>IBRAGIMOV</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>69073</t>
+          <t>36565</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Vilyam</t>
+          <t>Luca</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>IBRAGIMOV</t>
+          <t>INCOLLINGO</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -74735,61 +74695,61 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>36565</t>
+          <t>47633</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Luca</t>
+          <t>Karin</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>INCOLLINGO</t>
+          <t>JOHANSSON</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>47633</t>
+          <t>46375</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Karin</t>
+          <t>Denys</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>JOHANSSON</t>
+          <t>KAMERYLOV</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>46375</t>
+          <t>35713</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Denys</t>
+          <t>Stefan</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>KAMERYLOV</t>
+          <t>KIRAJ</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -74801,39 +74761,39 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>35713</t>
+          <t>118949</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Stefan</t>
+          <t>Inna</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>KIRAJ</t>
+          <t>KLINOVA</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>118949</t>
+          <t>44421</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Inna</t>
+          <t>Ivana</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>KLINOVA</t>
+          <t>KMETOVA</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -74845,39 +74805,39 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>44421</t>
+          <t>47675</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Ivana</t>
+          <t>Gerasim</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>KMETOVA</t>
+          <t>KOCHNEV</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>47675</t>
+          <t>42285</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Gerasim</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>KOCHNEV</t>
+          <t>VAN KOEVERDEN</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -74889,17 +74849,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>42285</t>
+          <t>35872</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Michal</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>VAN KOEVERDEN</t>
+          <t>KUDLA</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -74911,17 +74871,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>35872</t>
+          <t>35871</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Michal</t>
+          <t>Piotr</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>KUDLA</t>
+          <t>KULETA</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -74933,17 +74893,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>35871</t>
+          <t>42348</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Martin Trebbien Vestergaard</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>KULETA</t>
+          <t>LARSEN</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -74955,83 +74915,83 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>42348</t>
+          <t>46232</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Martin Trebbien Vestergaard</t>
+          <t>Irina</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>LARSEN</t>
+          <t>LAURIC</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>46232</t>
+          <t>42257</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Irina</t>
+          <t>Andres</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>LAURIC</t>
+          <t>LAZO</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>42257</t>
+          <t>55512</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Andres</t>
+          <t>Sun Ja</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>LAZO</t>
+          <t>LEE</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>55512</t>
+          <t>35562</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Sun Ja</t>
+          <t>Ana-Roxana</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>LEE</t>
+          <t>LEHACI</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -75043,39 +75003,39 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>35562</t>
+          <t>64070</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Ana-Roxana</t>
+          <t>Tony Gill</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>LEHACI</t>
+          <t>LESPOIR</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>64070</t>
+          <t>35719</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Tony Gill</t>
+          <t>Erik</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>LESPOIR</t>
+          <t>LEUE</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -75087,17 +75047,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>35719</t>
+          <t>52253</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Erik</t>
+          <t>Guiqiang</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>LEUE</t>
+          <t>LI</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -75109,12 +75069,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>52253</t>
+          <t>52169</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Guiqiang</t>
+          <t>Zhangli</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -75124,90 +75084,90 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>52169</t>
+          <t>60014</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Zhangli</t>
+          <t>Bo</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>LI</t>
+          <t>LIU</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>60014</t>
+          <t>42461</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Bo</t>
+          <t>Una Helen Bean</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>LIU</t>
+          <t>LOUNDER</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>42461</t>
+          <t>58229</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Una Helen Bean</t>
+          <t>Stuart</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>LOUNDER</t>
+          <t>MACLAREN</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>58229</t>
+          <t>53067</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Stuart</t>
+          <t>Roberto</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>MACLAREN</t>
+          <t>MAEHLER</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -75219,17 +75179,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>53067</t>
+          <t>42044</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Roberto</t>
+          <t>Vadzim</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>MAEHLER</t>
+          <t>MAKHNEU</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -75241,61 +75201,61 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>42044</t>
+          <t>36224</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Vadzim</t>
+          <t>Hayleigh-Jayne</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>MAKHNEU</t>
+          <t>MASON</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>36224</t>
+          <t>36226</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Hayleigh-Jayne</t>
+          <t>Edward</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>MASON</t>
+          <t>MCKEEVER</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>36226</t>
+          <t>47673</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Edward</t>
+          <t>Vadim</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>MCKEEVER</t>
+          <t>MENKOV</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -75307,17 +75267,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>47673</t>
+          <t>47252</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Vadim</t>
+          <t>Victor</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>MENKOV</t>
+          <t>MIHALACHI</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -75329,17 +75289,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>47252</t>
+          <t>52229</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Victor</t>
+          <t>Serik</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>MIHALACHI</t>
+          <t>MIRBEKOV</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -75351,17 +75311,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>52229</t>
+          <t>35721</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Serik</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>MIRBEKOV</t>
+          <t>MITTELSTEDT</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -75373,17 +75333,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>35721</t>
+          <t>52228</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Aleksey</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>MITTELSTEDT</t>
+          <t>MOCHALOV</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -75395,17 +75355,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>52228</t>
+          <t>42465</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Aleksey</t>
+          <t>Angus</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>MOCHALOV</t>
+          <t>MORTIMER</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -75417,61 +75377,61 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>42465</t>
+          <t>36562</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Angus</t>
+          <t>Norma</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>MORTIMER</t>
+          <t>MURABITO</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>36562</t>
+          <t>36798</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Norma</t>
+          <t>Ignas</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>MURABITO</t>
+          <t>NAVAKAUSKAS</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>36798</t>
+          <t>65873</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Ignas</t>
+          <t>Traian</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>NAVAKAUSKAS</t>
+          <t>NEAGU</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -75483,17 +75443,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>65873</t>
+          <t>36796</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Traian</t>
+          <t>Ricardas</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>NEAGU</t>
+          <t>NEKRIOSIUS</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -75505,17 +75465,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>36796</t>
+          <t>42466</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Ricardas</t>
+          <t>Mark William</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>NEKRIOSIUS</t>
+          <t>OLDERSHAW</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -75527,17 +75487,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>42466</t>
+          <t>36797</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Mark William</t>
+          <t>Andrej</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>OLDERSHAW</t>
+          <t>OLIJNIK</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -75549,17 +75509,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>36797</t>
+          <t>42769</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Andrej</t>
+          <t>Celso</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>OLIJNIK</t>
+          <t>DIAS DE OLIVEIRA JUNIOR</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -75571,17 +75531,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>42769</t>
+          <t>36635</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Celso</t>
+          <t>Ronilson Matias De</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>DIAS DE OLIVEIRA JUNIOR</t>
+          <t>OLIVEIRA</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -75593,39 +75553,39 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>36635</t>
+          <t>42467</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Ronilson Matias De</t>
+          <t>Genevieve Wendy Susan</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>OLIVEIRA</t>
+          <t>ORTON</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>42467</t>
+          <t>51871</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Genevieve Wendy Susan</t>
+          <t>Sofia</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>ORTON</t>
+          <t>PALDANIUS</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -75637,61 +75597,61 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>51871</t>
+          <t>41784</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Sofia</t>
+          <t>Laurens</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>PALDANIUS</t>
+          <t>PANNECOUCKE</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>41784</t>
+          <t>42059</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Laurens</t>
+          <t>Nadzeya</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>PANNECOUCKE</t>
+          <t>PAPOK</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>42059</t>
+          <t>42426</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Nadzeya</t>
+          <t>Cristina</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>PAPOK</t>
+          <t>PETRACCA</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -75703,39 +75663,39 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>42426</t>
+          <t>45847</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Cristina</t>
+          <t>Jesse</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>PETRACCA</t>
+          <t>PHILLIPS</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>45847</t>
+          <t>41991</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Jesse</t>
+          <t>Raman</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>PHILLIPS</t>
+          <t>PIATRUSHENKA</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -75747,39 +75707,39 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>41991</t>
+          <t>52294</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Raman</t>
+          <t>Ariela Cesar</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>PIATRUSHENKA</t>
+          <t>PINTO</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>52294</t>
+          <t>36313</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Ariela Cesar</t>
+          <t>Spela</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>PINTO</t>
+          <t>PONOMARENKO JANIC</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -75791,39 +75751,39 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>36313</t>
+          <t>42429</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Spela</t>
+          <t>Mauro</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>PONOMARENKO JANIC</t>
+          <t>PRA FLORIANI</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>42429</t>
+          <t>35863</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Mauro</t>
+          <t>Dawid</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>PRA FLORIANI</t>
+          <t>PUTTO</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -75835,17 +75795,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>35863</t>
+          <t>35724</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Dawid</t>
+          <t>Ronald</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>PUTTO</t>
+          <t>RAUHE</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -75857,17 +75817,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>35724</t>
+          <t>42468</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Ronald</t>
+          <t>Brady Daniel Heim</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>RAUHE</t>
+          <t>REARDON</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -75879,17 +75839,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>42468</t>
+          <t>35725</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Brady Daniel Heim</t>
+          <t>Erik</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>REARDON</t>
+          <t>REBSTOCK</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -75901,61 +75861,61 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>35725</t>
+          <t>52168</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Erik</t>
+          <t>Wenjun</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>REBSTOCK</t>
+          <t>REN</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>52168</t>
+          <t>47311</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Wenjun</t>
+          <t>Gilvan</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>REN</t>
+          <t>BITTENCOURT RIBEIRO</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>47311</t>
+          <t>36446</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Gilvan</t>
+          <t>Alberto</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>BITTENCOURT RIBEIRO</t>
+          <t>RICCHETTI</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -75967,17 +75927,17 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>36446</t>
+          <t>35862</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Alberto</t>
+          <t>Rafal</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>RICCHETTI</t>
+          <t>ROSOLSKI</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -75989,17 +75949,17 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>35862</t>
+          <t>36593</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Rafal</t>
+          <t>Aleksejs</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>ROSOLSKI</t>
+          <t>RUMJANCEVS</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -76011,17 +75971,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>36593</t>
+          <t>42471</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Aleksejs</t>
+          <t>Benjamin Rolph Mathew</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>RUMJANCEVS</t>
+          <t>RUSSELL</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -76033,17 +75993,17 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>42471</t>
+          <t>35981</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Benjamin Rolph Mathew</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>RUSSELL</t>
+          <t>SALBU</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -76055,39 +76015,39 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>35981</t>
+          <t>35561</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Yvonne</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>SALBU</t>
+          <t>SCHURING</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>35561</t>
+          <t>35560</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Yvonne</t>
+          <t>Viktoria</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>SCHURING</t>
+          <t>SCHWARZ</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -76099,17 +76059,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>35560</t>
+          <t>42573</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Viktoria</t>
+          <t>Natalya</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>SCHWARZ</t>
+          <t>SERGEYEVA</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -76121,17 +76081,17 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>42573</t>
+          <t>56337</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Natalya</t>
+          <t>Ekaterina</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>SERGEYEVA</t>
+          <t>SHUBINA</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -76143,39 +76103,39 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>56337</t>
+          <t>47312</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Ekaterina</t>
+          <t>Edson Isaias</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>SHUBINA</t>
+          <t>FREITAS DA SILVA</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>47312</t>
+          <t>45844</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Edson Isaias</t>
+          <t>David</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>FREITAS DA SILVA</t>
+          <t>SMITH</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -76187,17 +76147,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>45844</t>
+          <t>36634</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Erlon</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>SMITH</t>
+          <t>DE SOUZA SILVA</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -76209,17 +76169,17 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>36634</t>
+          <t>35776</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Erlon</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>DE SOUZA SILVA</t>
+          <t>STERBA</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -76231,17 +76191,17 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>35776</t>
+          <t>45793</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Murray</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>STERBA</t>
+          <t>STEWART</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -76253,17 +76213,17 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>45793</t>
+          <t>36792</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Murray</t>
+          <t>Jevgenij</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>STEWART</t>
+          <t>SHUKLIN</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -76275,17 +76235,17 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>36792</t>
+          <t>35934</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Jevgenij</t>
+          <t>Pawel</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>SHUKLIN</t>
+          <t>SZANDRACH</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -76297,61 +76257,61 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>35934</t>
+          <t>42484</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Pawel</t>
+          <t>Hannah Marie</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>SZANDRACH</t>
+          <t>VAUGHAN</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>42484</t>
+          <t>35729</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Hannah Marie</t>
+          <t>Ronald</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>VAUGHAN</t>
+          <t>VERCH</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>35729</t>
+          <t>46387</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Ronald</t>
+          <t>Vitaliy</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>VERCH</t>
+          <t>VERHELES</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -76363,39 +76323,39 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>46387</t>
+          <t>42883</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Vitaliy</t>
+          <t>Laurence</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>VERHELES</t>
+          <t>VINCENT-LAPOINTE</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>42883</t>
+          <t>36222</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Laurence</t>
+          <t>Jessica</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>VINCENT-LAPOINTE</t>
+          <t>WALKER</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -76407,17 +76367,17 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>36222</t>
+          <t>60075</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Jessica</t>
+          <t>Feng</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>WALKER</t>
+          <t>WANG</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -76429,17 +76389,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>60075</t>
+          <t>35733</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Feng</t>
+          <t>Conny</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>WANG</t>
+          <t>WASSMUTH</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -76451,39 +76411,39 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>35733</t>
+          <t>42443</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Conny</t>
+          <t>Barry</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>WASSMUTH</t>
+          <t>WATKINS</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>42443</t>
+          <t>35737</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Barry</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>WATKINS</t>
+          <t>WYLENZEK</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -76495,17 +76455,17 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>35737</t>
+          <t>42232</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Fabio</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>WYLENZEK</t>
+          <t>WYSS</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -76517,17 +76477,17 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>42232</t>
+          <t>42567</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Fabio</t>
+          <t>Alexandr</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>WYSS</t>
+          <t>YEMELYANOV</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -76539,12 +76499,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>42567</t>
+          <t>42562</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Alexandr</t>
+          <t>Mikhail</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -76561,17 +76521,17 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>42562</t>
+          <t>60015</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Mikhail</t>
+          <t>Peng</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>YEMELYANOV</t>
+          <t>ZHOU</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -76583,17 +76543,17 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>133041</t>
+          <t>52182</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Hong</t>
+          <t>Yu</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>ZHANG</t>
+          <t>ZHOU</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -76605,12 +76565,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>60015</t>
+          <t>61025</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Peng</t>
+          <t>Yubo</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -76619,50 +76579,6 @@
         </is>
       </c>
       <c r="D141" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>52182</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Yu</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>ZHOU</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>61025</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Yubo</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>ZHOU</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
         <is>
           <t>M</t>
         </is>

--- a/events/Duisburg_2010_WC/Duisburg_2010_WC_Results.xlsx
+++ b/events/Duisburg_2010_WC/Duisburg_2010_WC_Results.xlsx
@@ -3314,6 +3314,11 @@
           <t>0:43.185</t>
         </is>
       </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>52150</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -7084,6 +7089,11 @@
           <t>0:41.869</t>
         </is>
       </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>70017</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -8249,6 +8259,16 @@
           <t>0:42.133</t>
         </is>
       </c>
+      <c r="R125" t="inlineStr">
+        <is>
+          <t>36474</t>
+        </is>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>45015</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -12743,6 +12763,11 @@
           <t>3:40.779</t>
         </is>
       </c>
+      <c r="R196" t="inlineStr">
+        <is>
+          <t>47543</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -13918,6 +13943,11 @@
           <t>3:44.675</t>
         </is>
       </c>
+      <c r="R215" t="inlineStr">
+        <is>
+          <t>46407</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -14163,6 +14193,11 @@
           <t>3:38.483</t>
         </is>
       </c>
+      <c r="R219" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -15168,6 +15203,16 @@
           <t>4:50.771</t>
         </is>
       </c>
+      <c r="R235" t="inlineStr">
+        <is>
+          <t>36474</t>
+        </is>
+      </c>
+      <c r="S235" t="inlineStr">
+        <is>
+          <t>45015</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -16818,6 +16863,11 @@
           <t>3:46.773</t>
         </is>
       </c>
+      <c r="S261" t="inlineStr">
+        <is>
+          <t>70014</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -17003,6 +17053,11 @@
           <t>3:22.541</t>
         </is>
       </c>
+      <c r="R264" t="inlineStr">
+        <is>
+          <t>36232</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -17323,6 +17378,11 @@
           <t>3:26.691</t>
         </is>
       </c>
+      <c r="R269" t="inlineStr">
+        <is>
+          <t>42463</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -17928,6 +17988,11 @@
           <t>1:44.797</t>
         </is>
       </c>
+      <c r="S278" t="inlineStr">
+        <is>
+          <t>70017</t>
+        </is>
+      </c>
       <c r="T278" t="inlineStr">
         <is>
           <t>55512</t>
@@ -19208,6 +19273,11 @@
           <t>3:06.831</t>
         </is>
       </c>
+      <c r="S297" t="inlineStr">
+        <is>
+          <t>46407</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -21943,6 +22013,11 @@
           <t>0:43.069</t>
         </is>
       </c>
+      <c r="R341" t="inlineStr">
+        <is>
+          <t>52150</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -24993,6 +25068,11 @@
           <t>0:43.971</t>
         </is>
       </c>
+      <c r="S390" t="inlineStr">
+        <is>
+          <t>70017</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -25373,6 +25453,16 @@
           <t>0:42.407</t>
         </is>
       </c>
+      <c r="R396" t="inlineStr">
+        <is>
+          <t>36474</t>
+        </is>
+      </c>
+      <c r="S396" t="inlineStr">
+        <is>
+          <t>45015</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -29264,6 +29354,11 @@
           <t>0:41.781</t>
         </is>
       </c>
+      <c r="S457" t="inlineStr">
+        <is>
+          <t>70017</t>
+        </is>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -30928,6 +31023,11 @@
           <t>0:43.401</t>
         </is>
       </c>
+      <c r="R483" t="inlineStr">
+        <is>
+          <t>52150</t>
+        </is>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -35142,6 +35242,11 @@
           <t>3:27.651</t>
         </is>
       </c>
+      <c r="R548" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
@@ -36572,6 +36677,11 @@
           <t>3:35.985</t>
         </is>
       </c>
+      <c r="R571" t="inlineStr">
+        <is>
+          <t>47543</t>
+        </is>
+      </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
@@ -36697,6 +36807,11 @@
           <t>3:39.185</t>
         </is>
       </c>
+      <c r="R573" t="inlineStr">
+        <is>
+          <t>46407</t>
+        </is>
+      </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
@@ -37462,6 +37577,11 @@
           <t>3:17.303</t>
         </is>
       </c>
+      <c r="R585" t="inlineStr">
+        <is>
+          <t>36232</t>
+        </is>
+      </c>
     </row>
     <row r="586">
       <c r="A586" t="inlineStr">
@@ -39001,6 +39121,11 @@
       <c r="N609" t="n">
         <v>8</v>
       </c>
+      <c r="S609" t="inlineStr">
+        <is>
+          <t>70017</t>
+        </is>
+      </c>
       <c r="T609" t="inlineStr">
         <is>
           <t>55512</t>
@@ -40120,6 +40245,11 @@
           <t>3:38.177</t>
         </is>
       </c>
+      <c r="R626" t="inlineStr">
+        <is>
+          <t>47543</t>
+        </is>
+      </c>
     </row>
     <row r="627">
       <c r="A627" t="inlineStr">
@@ -42201,6 +42331,11 @@
           <t>3:32.373</t>
         </is>
       </c>
+      <c r="R658" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
     </row>
     <row r="659">
       <c r="A659" t="inlineStr">
@@ -44089,6 +44224,11 @@
           <t>3:24.675</t>
         </is>
       </c>
+      <c r="R687" t="inlineStr">
+        <is>
+          <t>36232</t>
+        </is>
+      </c>
     </row>
     <row r="688">
       <c r="A688" t="inlineStr">
@@ -45935,6 +46075,11 @@
           <t>1:51.236</t>
         </is>
       </c>
+      <c r="R715" t="inlineStr">
+        <is>
+          <t>52150</t>
+        </is>
+      </c>
     </row>
     <row r="716">
       <c r="A716" t="inlineStr">
@@ -46870,6 +47015,11 @@
           <t>1:42.753</t>
         </is>
       </c>
+      <c r="R730" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
     </row>
     <row r="731">
       <c r="A731" t="inlineStr">
@@ -50985,6 +51135,11 @@
           <t>1:49.301</t>
         </is>
       </c>
+      <c r="S796" t="inlineStr">
+        <is>
+          <t>70017</t>
+        </is>
+      </c>
     </row>
     <row r="797">
       <c r="A797" t="inlineStr">
@@ -52750,6 +52905,11 @@
           <t>1:33.569</t>
         </is>
       </c>
+      <c r="R824" t="inlineStr">
+        <is>
+          <t>36232</t>
+        </is>
+      </c>
     </row>
     <row r="825">
       <c r="A825" t="inlineStr">
@@ -53590,6 +53750,11 @@
           <t>1:44.303</t>
         </is>
       </c>
+      <c r="S837" t="inlineStr">
+        <is>
+          <t>70014</t>
+        </is>
+      </c>
     </row>
     <row r="838">
       <c r="A838" t="inlineStr">
@@ -54552,6 +54717,16 @@
           <t>1:48.873</t>
         </is>
       </c>
+      <c r="R852" t="inlineStr">
+        <is>
+          <t>36474</t>
+        </is>
+      </c>
+      <c r="S852" t="inlineStr">
+        <is>
+          <t>45015</t>
+        </is>
+      </c>
     </row>
     <row r="853">
       <c r="A853" t="inlineStr">
@@ -55172,6 +55347,11 @@
           <t>1:50.539</t>
         </is>
       </c>
+      <c r="R862" t="inlineStr">
+        <is>
+          <t>52150</t>
+        </is>
+      </c>
     </row>
     <row r="863">
       <c r="A863" t="inlineStr">
@@ -57062,6 +57242,11 @@
           <t>1:39.295</t>
         </is>
       </c>
+      <c r="R892" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
     </row>
     <row r="893">
       <c r="A893" t="inlineStr">
@@ -60987,6 +61172,11 @@
           <t>1:32.665</t>
         </is>
       </c>
+      <c r="R955" t="inlineStr">
+        <is>
+          <t>36232</t>
+        </is>
+      </c>
     </row>
     <row r="956">
       <c r="A956" t="inlineStr">
@@ -62152,6 +62342,16 @@
           <t>1:44.855</t>
         </is>
       </c>
+      <c r="R973" t="inlineStr">
+        <is>
+          <t>36474</t>
+        </is>
+      </c>
+      <c r="S973" t="inlineStr">
+        <is>
+          <t>45015</t>
+        </is>
+      </c>
     </row>
     <row r="974">
       <c r="A974" t="inlineStr">
@@ -63550,6 +63750,11 @@
           <t>1:37.559</t>
         </is>
       </c>
+      <c r="R995" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
     </row>
     <row r="996">
       <c r="A996" t="inlineStr">
@@ -65279,6 +65484,11 @@
           <t>1:30.413</t>
         </is>
       </c>
+      <c r="R1022" t="inlineStr">
+        <is>
+          <t>36232</t>
+        </is>
+      </c>
     </row>
     <row r="1023">
       <c r="A1023" t="inlineStr">
@@ -66428,6 +66638,11 @@
           <t>2:58.233</t>
         </is>
       </c>
+      <c r="S1039" t="inlineStr">
+        <is>
+          <t>46407</t>
+        </is>
+      </c>
     </row>
     <row r="1040">
       <c r="A1040" t="inlineStr">
@@ -66746,6 +66961,11 @@
       <c r="P1044" t="inlineStr">
         <is>
           <t>1:51.575</t>
+        </is>
+      </c>
+      <c r="R1044" t="inlineStr">
+        <is>
+          <t>52150</t>
         </is>
       </c>
     </row>
@@ -73479,7 +73699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D141"/>
+  <dimension ref="A1:D151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76584,6 +76804,226 @@
         </is>
       </c>
     </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>36232</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Jonathan</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>BOYTON</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>36474</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Dongjin</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>SHIN</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Aleh</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>YURENIA</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>42463</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Chris</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>MEHAK</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>45015</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Taeeun</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>KIM</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>46407</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Vitalii</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>TSURKAN</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>47543</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Ahmadreza</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>TALEBIAN</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>52150</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Jo</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>BRIGDEN-JONES</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>70014</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Minkyu</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>CHOI</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>70017</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Gukjoo</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>KIM</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/Duisburg_2010_WC/Duisburg_2010_WC_Results.xlsx
+++ b/events/Duisburg_2010_WC/Duisburg_2010_WC_Results.xlsx
@@ -3749,6 +3749,11 @@
           <t>0:44.647</t>
         </is>
       </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>133041</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -16993,6 +16998,11 @@
           <t>3:21.389</t>
         </is>
       </c>
+      <c r="R263" t="inlineStr">
+        <is>
+          <t>41785</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -17718,6 +17728,11 @@
           <t>1:38.123</t>
         </is>
       </c>
+      <c r="S274" t="inlineStr">
+        <is>
+          <t>133041</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -22333,6 +22348,11 @@
           <t>0:44.931</t>
         </is>
       </c>
+      <c r="R346" t="inlineStr">
+        <is>
+          <t>133041</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -38097,6 +38117,11 @@
           <t>3:16.555</t>
         </is>
       </c>
+      <c r="R593" t="inlineStr">
+        <is>
+          <t>41785</t>
+        </is>
+      </c>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
@@ -38654,6 +38679,11 @@
           <t>1:36.651</t>
         </is>
       </c>
+      <c r="S602" t="inlineStr">
+        <is>
+          <t>133041</t>
+        </is>
+      </c>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
@@ -43904,6 +43934,11 @@
           <t>3:19.525</t>
         </is>
       </c>
+      <c r="R682" t="inlineStr">
+        <is>
+          <t>41785</t>
+        </is>
+      </c>
     </row>
     <row r="683">
       <c r="A683" t="inlineStr">
@@ -44860,6 +44895,11 @@
       <c r="P696" t="inlineStr">
         <is>
           <t>1:41.745</t>
+        </is>
+      </c>
+      <c r="S696" t="inlineStr">
+        <is>
+          <t>133041</t>
         </is>
       </c>
     </row>
@@ -73699,7 +73739,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D151"/>
+  <dimension ref="A1:D153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77024,6 +77064,50 @@
         </is>
       </c>
     </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>41785</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Olivier</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>CAUWENBERGH</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>133041</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Hong</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>ZHANG</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/Duisburg_2010_WC/Duisburg_2010_WC_Results.xlsx
+++ b/events/Duisburg_2010_WC/Duisburg_2010_WC_Results.xlsx
@@ -3749,11 +3749,6 @@
           <t>0:44.647</t>
         </is>
       </c>
-      <c r="R53" t="inlineStr">
-        <is>
-          <t>133041</t>
-        </is>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -16998,11 +16993,6 @@
           <t>3:21.389</t>
         </is>
       </c>
-      <c r="R263" t="inlineStr">
-        <is>
-          <t>41785</t>
-        </is>
-      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -17728,11 +17718,6 @@
           <t>1:38.123</t>
         </is>
       </c>
-      <c r="S274" t="inlineStr">
-        <is>
-          <t>133041</t>
-        </is>
-      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -22348,11 +22333,6 @@
           <t>0:44.931</t>
         </is>
       </c>
-      <c r="R346" t="inlineStr">
-        <is>
-          <t>133041</t>
-        </is>
-      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -38117,11 +38097,6 @@
           <t>3:16.555</t>
         </is>
       </c>
-      <c r="R593" t="inlineStr">
-        <is>
-          <t>41785</t>
-        </is>
-      </c>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
@@ -38679,11 +38654,6 @@
           <t>1:36.651</t>
         </is>
       </c>
-      <c r="S602" t="inlineStr">
-        <is>
-          <t>133041</t>
-        </is>
-      </c>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
@@ -43934,11 +43904,6 @@
           <t>3:19.525</t>
         </is>
       </c>
-      <c r="R682" t="inlineStr">
-        <is>
-          <t>41785</t>
-        </is>
-      </c>
     </row>
     <row r="683">
       <c r="A683" t="inlineStr">
@@ -44895,11 +44860,6 @@
       <c r="P696" t="inlineStr">
         <is>
           <t>1:41.745</t>
-        </is>
-      </c>
-      <c r="S696" t="inlineStr">
-        <is>
-          <t>133041</t>
         </is>
       </c>
     </row>
@@ -73739,7 +73699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D153"/>
+  <dimension ref="A1:D151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77064,50 +77024,6 @@
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>41785</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>Olivier</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>CAUWENBERGH</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>133041</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>Hong</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>ZHANG</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/Duisburg_2010_WC/Duisburg_2010_WC_Results.xlsx
+++ b/events/Duisburg_2010_WC/Duisburg_2010_WC_Results.xlsx
@@ -5904,6 +5904,11 @@
           <t>0:42.373</t>
         </is>
       </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>46385</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -8124,6 +8129,11 @@
           <t>0:40.293</t>
         </is>
       </c>
+      <c r="R123" t="inlineStr">
+        <is>
+          <t>51786</t>
+        </is>
+      </c>
       <c r="S123" t="inlineStr">
         <is>
           <t>42447</t>
@@ -8329,6 +8339,11 @@
           <t>0:39.655</t>
         </is>
       </c>
+      <c r="R126" t="inlineStr">
+        <is>
+          <t>36384</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -15338,6 +15353,11 @@
           <t>3:42.867</t>
         </is>
       </c>
+      <c r="R237" t="inlineStr">
+        <is>
+          <t>36384</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -23058,6 +23078,11 @@
           <t>0:42.105</t>
         </is>
       </c>
+      <c r="R358" t="inlineStr">
+        <is>
+          <t>46385</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -25328,6 +25353,11 @@
           <t>0:40.704</t>
         </is>
       </c>
+      <c r="R394" t="inlineStr">
+        <is>
+          <t>51786</t>
+        </is>
+      </c>
       <c r="S394" t="inlineStr">
         <is>
           <t>42447</t>
@@ -31539,6 +31569,11 @@
           <t>0:41.655</t>
         </is>
       </c>
+      <c r="R491" t="inlineStr">
+        <is>
+          <t>46385</t>
+        </is>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -32975,6 +33010,11 @@
           <t>0:38.909</t>
         </is>
       </c>
+      <c r="R513" t="inlineStr">
+        <is>
+          <t>36384</t>
+        </is>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -33387,6 +33427,11 @@
           <t>0:40.895</t>
         </is>
       </c>
+      <c r="R519" t="inlineStr">
+        <is>
+          <t>51786</t>
+        </is>
+      </c>
       <c r="S519" t="inlineStr">
         <is>
           <t>42447</t>
@@ -43239,6 +43284,11 @@
           <t>3:35.871</t>
         </is>
       </c>
+      <c r="R672" t="inlineStr">
+        <is>
+          <t>36384</t>
+        </is>
+      </c>
     </row>
     <row r="673">
       <c r="A673" t="inlineStr">
@@ -49875,6 +49925,11 @@
           <t>1:55.489</t>
         </is>
       </c>
+      <c r="R776" t="inlineStr">
+        <is>
+          <t>46385</t>
+        </is>
+      </c>
     </row>
     <row r="777">
       <c r="A777" t="inlineStr">
@@ -54215,6 +54270,11 @@
           <t>1:49.951</t>
         </is>
       </c>
+      <c r="R844" t="inlineStr">
+        <is>
+          <t>51786</t>
+        </is>
+      </c>
       <c r="S844" t="inlineStr">
         <is>
           <t>42447</t>
@@ -54337,6 +54397,11 @@
           <t>1:40.823</t>
         </is>
       </c>
+      <c r="R846" t="inlineStr">
+        <is>
+          <t>36384</t>
+        </is>
+      </c>
     </row>
     <row r="847">
       <c r="A847" t="inlineStr">
@@ -59357,6 +59422,11 @@
           <t>1:50.293</t>
         </is>
       </c>
+      <c r="R926" t="inlineStr">
+        <is>
+          <t>46385</t>
+        </is>
+      </c>
     </row>
     <row r="927">
       <c r="A927" t="inlineStr">
@@ -62472,6 +62542,11 @@
           <t>1:46.279</t>
         </is>
       </c>
+      <c r="R975" t="inlineStr">
+        <is>
+          <t>51786</t>
+        </is>
+      </c>
       <c r="S975" t="inlineStr">
         <is>
           <t>42447</t>
@@ -68392,6 +68467,11 @@
           <t>1:59.807</t>
         </is>
       </c>
+      <c r="R1066" t="inlineStr">
+        <is>
+          <t>46385</t>
+        </is>
+      </c>
     </row>
     <row r="1067">
       <c r="A1067" t="inlineStr">
@@ -69665,6 +69745,11 @@
           <t>1:40.913</t>
         </is>
       </c>
+      <c r="R1085" t="inlineStr">
+        <is>
+          <t>36384</t>
+        </is>
+      </c>
     </row>
     <row r="1086">
       <c r="A1086" t="inlineStr">
@@ -72011,6 +72096,11 @@
       <c r="T1119" t="inlineStr">
         <is>
           <t>42466</t>
+        </is>
+      </c>
+      <c r="U1119" t="inlineStr">
+        <is>
+          <t>51786</t>
         </is>
       </c>
     </row>
@@ -73699,7 +73789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D151"/>
+  <dimension ref="A1:D154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77024,6 +77114,72 @@
         </is>
       </c>
     </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>46385</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Oleksandr</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>MAKSIMCHUK</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>51786</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Antoine</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>MEHNIER</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>36384</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Sergiy</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>BEZUGLIR</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/Duisburg_2010_WC/Duisburg_2010_WC_Results.xlsx
+++ b/events/Duisburg_2010_WC/Duisburg_2010_WC_Results.xlsx
@@ -4984,6 +4984,11 @@
           <t>0:43.281</t>
         </is>
       </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>36633</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -23758,6 +23763,11 @@
           <t>0:42.419</t>
         </is>
       </c>
+      <c r="R369" t="inlineStr">
+        <is>
+          <t>36633</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -28556,6 +28566,11 @@
           <t>0:42.467</t>
         </is>
       </c>
+      <c r="R444" t="inlineStr">
+        <is>
+          <t>36633</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -72163,6 +72178,11 @@
       <c r="P1120" t="inlineStr">
         <is>
           <t>3:00.141</t>
+        </is>
+      </c>
+      <c r="S1120" t="inlineStr">
+        <is>
+          <t>36633</t>
         </is>
       </c>
       <c r="T1120" t="inlineStr">
@@ -73789,7 +73809,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D154"/>
+  <dimension ref="A1:D155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77180,6 +77200,28 @@
         </is>
       </c>
     </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>36633</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Nivalter</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>SANTOS</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
